--- a/artfynd/A 56956-2021 artfynd.xlsx
+++ b/artfynd/A 56956-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56956-2021 artfynd.xlsx
+++ b/artfynd/A 56956-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1734147</v>
+        <v>168289</v>
       </c>
       <c r="B2" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673470.5235017354</v>
+        <v>673420</v>
       </c>
       <c r="R2" t="n">
-        <v>6683024.204749956</v>
+        <v>6683047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>11 ex under gammelgran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,40 +791,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1726879</v>
+        <v>185651</v>
       </c>
       <c r="B3" t="n">
-        <v>85076</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -851,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673470.5235017354</v>
+        <v>673559</v>
       </c>
       <c r="R3" t="n">
-        <v>6683024.204749956</v>
+        <v>6682878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,24 +868,14 @@
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>7 ex under gran längs en gammal körväg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,42 +911,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>168289</v>
+        <v>940263</v>
       </c>
       <c r="B4" t="n">
-        <v>85147</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -986,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673419.6501791457</v>
+        <v>673632</v>
       </c>
       <c r="R4" t="n">
-        <v>6683046.648661576</v>
+        <v>6682706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,27 +985,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>11 ex under gammelgran</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1009,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>BAVI05</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1072,15 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1734146</v>
+        <v>1151602</v>
       </c>
       <c r="B5" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1117,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673558.6513893852</v>
+        <v>673471</v>
       </c>
       <c r="R5" t="n">
-        <v>6682878.224930345</v>
+        <v>6683024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,24 +1109,14 @@
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några grupper</t>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1130,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,12 +1155,7 @@
         <v>1349743</v>
       </c>
       <c r="B6" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673449.9331027269</v>
+        <v>673450</v>
       </c>
       <c r="R6" t="n">
-        <v>6683006.816962675</v>
+        <v>6683007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,19 +1229,9 @@
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1338,37 +1272,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1666913</v>
+        <v>1726879</v>
       </c>
       <c r="B7" t="n">
-        <v>88952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5754</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1383,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>673444.8928941421</v>
+        <v>673471</v>
       </c>
       <c r="R7" t="n">
-        <v>6683008.069124406</v>
+        <v>6683024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1416,24 +1345,14 @@
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2004-10-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig under gammelgran</t>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,42 +1388,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>185651</v>
+        <v>69517686</v>
       </c>
       <c r="B8" t="n">
-        <v>85176</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>445</v>
+        <v>4189</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1514,14 +1428,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NBI ca 700 m SV Rovsättra, Upl</t>
+          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673558.6513893852</v>
+        <v>673547</v>
       </c>
       <c r="R8" t="n">
-        <v>6682878.224930345</v>
+        <v>6682850</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,27 +1462,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>7 ex under gran längs en gammal körväg</t>
+          <t>1 fjolårs-ex. under gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,65 +1483,55 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Uppföljning av skyddade områden</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1326565</v>
+        <v>69528020</v>
       </c>
       <c r="B9" t="n">
-        <v>90318</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1645,14 +1539,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NBI ca 700 m SV Rovsättra, Upl</t>
+          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673470.5235017354</v>
+        <v>673563</v>
       </c>
       <c r="R9" t="n">
-        <v>6683024.204749956</v>
+        <v>6682795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,27 +1573,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>Ca. 50 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1711,64 +1595,59 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av lövträd.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Uppföljning av skyddade områden</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1151602</v>
+        <v>69528021</v>
       </c>
       <c r="B10" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1776,14 +1655,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NBI ca 700 m SV Rovsättra, Upl</t>
+          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673470.5235017354</v>
+        <v>673547</v>
       </c>
       <c r="R10" t="n">
-        <v>6683024.204749956</v>
+        <v>6682865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,27 +1689,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2004-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>Ca. 5 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,40 +1710,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Uppföljning av skyddade områden</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69517686</v>
+        <v>1326565</v>
       </c>
       <c r="B11" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,28 +1737,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1911,14 +1762,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
+          <t>NBI ca 700 m SV Rovsättra, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673547.028028117</v>
+        <v>673471</v>
       </c>
       <c r="R11" t="n">
-        <v>6682850.322586423</v>
+        <v>6683024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,27 +1796,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 fjolårs-ex. under gran.</t>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,31 +1817,35 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69528020</v>
+        <v>1666913</v>
       </c>
       <c r="B12" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,28 +1853,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2037,14 +1878,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
+          <t>NBI ca 700 m SV Rovsättra, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673562.592020641</v>
+        <v>673445</v>
       </c>
       <c r="R12" t="n">
-        <v>6682795.368500255</v>
+        <v>6683008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,27 +1912,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca. 50 ex.</t>
+          <t>Riklig under gammelgran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,35 +1934,34 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av lövträd.</t>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69528021</v>
+        <v>1734146</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,28 +1969,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2168,14 +1994,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rovsättra 5 km SSO om Valö kyrka, Upl</t>
+          <t>NBI ca 700 m SV Rovsättra, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673546.8171518191</v>
+        <v>673559</v>
       </c>
       <c r="R13" t="n">
-        <v>6682865.230522838</v>
+        <v>6682878</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,27 +2028,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2004-07-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-10-22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca. 5 ex.</t>
+          <t>Några grupper</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2233,19 +2049,144 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1734147</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NBI ca 700 m SV Rovsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>673471</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6683024</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2004-10-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2004-10-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka ex</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56956-2021 artfynd.xlsx
+++ b/artfynd/A 56956-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/185651</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/940263</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1151602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1349743</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1385,6 +1415,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1726879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1496,6 +1531,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69517686</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69528020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69528021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1839,6 +1889,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1326565</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1955,6 +2010,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1666913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2071,6 +2131,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1734146</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2187,8 +2252,28 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1734147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>